--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.22648779496608</v>
+        <v>7.674304266681989</v>
       </c>
       <c r="D2" t="n">
-        <v>28.82166815685756</v>
+        <v>4.683521075489354</v>
       </c>
       <c r="E2" t="n">
-        <v>13.40637671747408</v>
+        <v>2.178536216589538</v>
       </c>
       <c r="F2" t="n">
-        <v>8.169052492606179</v>
+        <v>1.327471030048504</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.74490660786446</v>
+        <v>3.858547323777974</v>
       </c>
       <c r="D3" t="n">
-        <v>23.76341396786983</v>
+        <v>3.861554769778848</v>
       </c>
       <c r="E3" t="n">
-        <v>13.40637671747408</v>
+        <v>2.178536216589538</v>
       </c>
       <c r="F3" t="n">
-        <v>8.169052492606179</v>
+        <v>1.327471030048504</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.59978006928717</v>
+        <v>3.509964261259166</v>
       </c>
       <c r="D4" t="n">
-        <v>21.16391735518287</v>
+        <v>3.439136570217216</v>
       </c>
       <c r="E4" t="n">
-        <v>13.40637671747408</v>
+        <v>2.178536216589538</v>
       </c>
       <c r="F4" t="n">
-        <v>8.169052492606179</v>
+        <v>1.327471030048504</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>53.30845243900912</v>
+        <v>8.662623521338981</v>
       </c>
       <c r="D5" t="n">
-        <v>37.56275705432896</v>
+        <v>6.103948021328455</v>
       </c>
       <c r="E5" t="n">
-        <v>13.40637671747408</v>
+        <v>2.178536216589538</v>
       </c>
       <c r="F5" t="n">
-        <v>8.169052492606179</v>
+        <v>1.327471030048504</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.839264110549872</v>
+        <v>1.273880417964354</v>
       </c>
       <c r="D6" t="n">
-        <v>21.12131567523261</v>
+        <v>3.432213797225299</v>
       </c>
       <c r="E6" t="n">
-        <v>13.40637671747408</v>
+        <v>2.178536216589538</v>
       </c>
       <c r="F6" t="n">
-        <v>8.169052492606179</v>
+        <v>1.327471030048504</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.09977089122079</v>
+        <v>5.378712769823378</v>
       </c>
       <c r="D7" t="n">
-        <v>6.576611419524923</v>
+        <v>1.0686993556728</v>
       </c>
       <c r="E7" t="n">
-        <v>13.40637671747408</v>
+        <v>2.178536216589538</v>
       </c>
       <c r="F7" t="n">
-        <v>8.169052492606179</v>
+        <v>1.327471030048504</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.32329102121302</v>
+        <v>6.715034790947117</v>
       </c>
       <c r="D8" t="n">
-        <v>25.09792854472402</v>
+        <v>4.078413388517654</v>
       </c>
       <c r="E8" t="n">
-        <v>13.40637671747408</v>
+        <v>2.178536216589538</v>
       </c>
       <c r="F8" t="n">
-        <v>8.169052492606179</v>
+        <v>1.327471030048504</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>50.33974893232691</v>
+        <v>8.180209201503123</v>
       </c>
       <c r="D9" t="n">
-        <v>22.75152529743796</v>
+        <v>3.697122860833668</v>
       </c>
       <c r="E9" t="n">
-        <v>13.40637671747408</v>
+        <v>2.178536216589538</v>
       </c>
       <c r="F9" t="n">
-        <v>8.169052492606179</v>
+        <v>1.327471030048504</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.51024491894205</v>
+        <v>5.607914799328083</v>
       </c>
       <c r="D10" t="n">
-        <v>8.550348335288863</v>
+        <v>1.38943160448444</v>
       </c>
       <c r="E10" t="n">
-        <v>13.40637671747408</v>
+        <v>2.178536216589538</v>
       </c>
       <c r="F10" t="n">
-        <v>8.169052492606179</v>
+        <v>1.327471030048504</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>36.32707849946908</v>
+        <v>5.903150256163726</v>
       </c>
       <c r="D11" t="n">
-        <v>18.08503155724757</v>
+        <v>2.938817628052731</v>
       </c>
       <c r="E11" t="n">
-        <v>13.40637671747408</v>
+        <v>2.178536216589538</v>
       </c>
       <c r="F11" t="n">
-        <v>8.169052492606179</v>
+        <v>1.327471030048504</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>48.50771405813444</v>
+        <v>7.882503534446847</v>
       </c>
       <c r="D12" t="n">
-        <v>20.45861351241382</v>
+        <v>3.324524695767245</v>
       </c>
       <c r="E12" t="n">
-        <v>13.40637671747408</v>
+        <v>2.178536216589538</v>
       </c>
       <c r="F12" t="n">
-        <v>8.169052492606179</v>
+        <v>1.327471030048504</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
